--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.138.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.138.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0138.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0138.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€, or other</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: -； and</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: By a person entitled to haveâ€™a new trustee appointed</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L32: symbol-only separator/garbage line :: 11.</t>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -676,14 +680,10 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief ; pray subpÃ¦na.)</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ; and</t>
-        </is>
-      </c>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一, or other</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -739,14 +739,10 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Ã¦ na.)</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -762,7 +758,7 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
+          <t>L99: punctuation artifact: double/multiple hyphen :: f - -----—,</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -786,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -800,16 +796,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: judgment creditors, as in the 6th articleâ€”with the addition-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”except that the words referring to real assets of de- Within the</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -856,11 +844,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: judgment creditors, as in the 6th articleâ€”with the addi- orders.</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -903,16 +887,12 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: A</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -955,7 +935,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 8</t>
+          <t>L105: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -996,7 +976,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L110: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -1017,12 +1001,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1061,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1095,7 +1079,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
